--- a/sensitivity_analysis/omega_sensitivity/model_sensitivity/graphs/SS_Comparison_omega_val.xlsx
+++ b/sensitivity_analysis/omega_sensitivity/model_sensitivity/graphs/SS_Comparison_omega_val.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="79" uniqueCount="79">
   <si>
     <t>Variable</t>
   </si>
@@ -181,9 +181,6 @@
   </si>
   <si>
     <t>xi</t>
-  </si>
-  <si>
-    <t>spread</t>
   </si>
   <si>
     <t>U_H</t>
@@ -298,11 +295,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" customWidth="true"/>
+    <col min="2" max="2" width="15.5703125" customWidth="true"/>
     <col min="3" max="3" width="15.7109375" customWidth="true"/>
     <col min="4" max="4" width="15.5703125" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
@@ -313,16 +310,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="D1" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="E1" s="0" t="s">
         <v>78</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2">
@@ -330,16 +327,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>0.14388224519942355</v>
+        <v>0.22044594474004953</v>
       </c>
       <c r="C2" s="0">
-        <v>0.14428960910359803</v>
+        <v>0.22098779215444392</v>
       </c>
       <c r="D2" s="0">
-        <v>0.14395501349384399</v>
+        <v>0.2204090356290708</v>
       </c>
       <c r="E2" s="0">
-        <v>0.14431579164182867</v>
+        <v>0.22098393040111511</v>
       </c>
     </row>
     <row r="3">
@@ -347,16 +344,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>0.32429464325123636</v>
+        <v>0.32141413782875433</v>
       </c>
       <c r="C3" s="0">
-        <v>0.32376524968509607</v>
+        <v>0.32069140954111869</v>
       </c>
       <c r="D3" s="0">
-        <v>0.32424677725009959</v>
+        <v>0.32146028891271994</v>
       </c>
       <c r="E3" s="0">
-        <v>0.32375176618313678</v>
+        <v>0.32069562327025308</v>
       </c>
     </row>
     <row r="4">
@@ -364,16 +361,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>0.046041577048937063</v>
+        <v>0.11337486336832386</v>
       </c>
       <c r="C4" s="0">
-        <v>0.018965932139719761</v>
+        <v>0.033807886794255192</v>
       </c>
       <c r="D4" s="0">
-        <v>0.046104103534410232</v>
+        <v>0.11265809873446334</v>
       </c>
       <c r="E4" s="0">
-        <v>0.018926389752057404</v>
+        <v>0.032677327080453948</v>
       </c>
     </row>
     <row r="5">
@@ -381,16 +378,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>7.2022737342301696e-06</v>
+        <v>3.0912574842893919e-05</v>
       </c>
       <c r="C5" s="0">
-        <v>0.029008268654093793</v>
+        <v>0.092170723816412919</v>
       </c>
       <c r="D5" s="0">
-        <v>7.16618582449992e-06</v>
+        <v>3.2170918109320237e-05</v>
       </c>
       <c r="E5" s="0">
-        <v>0.029050591757925754</v>
+        <v>0.093304831111441291</v>
       </c>
     </row>
     <row r="6">
@@ -398,16 +395,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>0.046048658269278571</v>
+        <v>0.11340364667618352</v>
       </c>
       <c r="C6" s="0">
-        <v>0.047762013458020468</v>
+        <v>0.12313954699715227</v>
       </c>
       <c r="D6" s="0">
-        <v>0.046111152400804475</v>
+        <v>0.11268788413230946</v>
       </c>
       <c r="E6" s="0">
-        <v>0.047761299790543416</v>
+        <v>0.12290560734922572</v>
       </c>
     </row>
     <row r="7">
@@ -415,16 +412,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>0.40603746672002755</v>
+        <v>0.38778758045286177</v>
       </c>
       <c r="C7" s="0">
-        <v>0.40558179556450591</v>
+        <v>0.38760108113848307</v>
       </c>
       <c r="D7" s="0">
-        <v>0.40586702183725282</v>
+        <v>0.38780823045084206</v>
       </c>
       <c r="E7" s="0">
-        <v>0.40551373463118023</v>
+        <v>0.38760470204647768</v>
       </c>
     </row>
     <row r="8">
@@ -432,16 +429,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>0.33210491294422384</v>
+        <v>0.32060759189760435</v>
       </c>
       <c r="C8" s="0">
-        <v>0.33254650563002836</v>
+        <v>0.32059184182600731</v>
       </c>
       <c r="D8" s="0">
-        <v>0.33228645883497171</v>
+        <v>0.32060055712741636</v>
       </c>
       <c r="E8" s="0">
-        <v>0.33261977471714738</v>
+        <v>0.32058960626430605</v>
       </c>
     </row>
     <row r="9">
@@ -449,16 +446,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>1.6211586731585348</v>
+        <v>1.6725579771688905</v>
       </c>
       <c r="C9" s="0">
-        <v>1.6202330166730439</v>
+        <v>1.6803615600989337</v>
       </c>
       <c r="D9" s="0">
-        <v>1.6207444156104367</v>
+        <v>1.6730842976829556</v>
       </c>
       <c r="E9" s="0">
-        <v>1.6200633611066382</v>
+        <v>1.6806138365404657</v>
       </c>
     </row>
     <row r="10">
@@ -466,16 +463,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>0.86236716120720802</v>
+        <v>3.764021575452098</v>
       </c>
       <c r="C10" s="0">
-        <v>0.85022243459771296</v>
+        <v>3.7525626470097779</v>
       </c>
       <c r="D10" s="0">
-        <v>0.85733440269919692</v>
+        <v>3.7637300964870382</v>
       </c>
       <c r="E10" s="0">
-        <v>0.84819322843792322</v>
+        <v>3.7523335683502901</v>
       </c>
     </row>
     <row r="11">
@@ -483,16 +480,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>11.621472268588802</v>
+        <v>0.46701336213906386</v>
       </c>
       <c r="C11" s="0">
-        <v>11.671597051845797</v>
+        <v>0.46023917018812383</v>
       </c>
       <c r="D11" s="0">
-        <v>11.647619099223762</v>
+        <v>0.46659432872018924</v>
       </c>
       <c r="E11" s="0">
-        <v>11.682133267894054</v>
+        <v>0.46003274562512586</v>
       </c>
     </row>
     <row r="12">
@@ -500,16 +497,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>4.3516382836464587</v>
+        <v>3.3097680913244374</v>
       </c>
       <c r="C12" s="0">
-        <v>4.4062520162904226</v>
+        <v>3.2785537596042653</v>
       </c>
       <c r="D12" s="0">
-        <v>4.3760794789842397</v>
+        <v>3.3076628092681766</v>
       </c>
       <c r="E12" s="0">
-        <v>4.4162616947083535</v>
+        <v>3.2775446538381368</v>
       </c>
     </row>
     <row r="13">
@@ -517,16 +514,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>49.037711338318424</v>
+        <v>14.489057422092559</v>
       </c>
       <c r="C13" s="0">
-        <v>48.244155609512525</v>
+        <v>14.380357534985771</v>
       </c>
       <c r="D13" s="0">
-        <v>48.738278970443233</v>
+        <v>14.491469037685288</v>
       </c>
       <c r="E13" s="0">
-        <v>48.124321217438137</v>
+        <v>14.379423482441686</v>
       </c>
     </row>
     <row r="14">
@@ -534,16 +531,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>402.69838355200898</v>
+        <v>32.766084020211444</v>
       </c>
       <c r="C14" s="0">
-        <v>403.09051505301409</v>
+        <v>32.739232580655198</v>
       </c>
       <c r="D14" s="0">
-        <v>402.88496034704258</v>
+        <v>32.767263279633781</v>
       </c>
       <c r="E14" s="0">
-        <v>403.16665358112334</v>
+        <v>32.739234747406698</v>
       </c>
     </row>
     <row r="15">
@@ -551,16 +548,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>10.067459588800224</v>
+        <v>0.81915210050528586</v>
       </c>
       <c r="C15" s="0">
-        <v>10.077262876325353</v>
+        <v>0.81848081451638011</v>
       </c>
       <c r="D15" s="0">
-        <v>10.072124008676122</v>
+        <v>0.81918158199084457</v>
       </c>
       <c r="E15" s="0">
-        <v>10.079166339528083</v>
+        <v>0.81848086868516745</v>
       </c>
     </row>
     <row r="16">
@@ -568,16 +565,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>9.3605973343014917</v>
+        <v>0.77403060902948795</v>
       </c>
       <c r="C16" s="0">
-        <v>9.4212947302050889</v>
+        <v>0.76886942746758069</v>
       </c>
       <c r="D16" s="0">
-        <v>9.389048412928469</v>
+        <v>0.77354011756267749</v>
       </c>
       <c r="E16" s="0">
-        <v>9.4326912392283209</v>
+        <v>0.76866474911922478</v>
       </c>
     </row>
     <row r="17">
@@ -585,16 +582,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>0.41332972613047364</v>
+        <v>0.31203934076507589</v>
       </c>
       <c r="C17" s="0">
-        <v>0.41372507354295562</v>
+        <v>0.31155824555142753</v>
       </c>
       <c r="D17" s="0">
-        <v>0.41351973927375435</v>
+        <v>0.31198724286689117</v>
       </c>
       <c r="E17" s="0">
-        <v>0.41380075276806838</v>
+        <v>0.31153712058166122</v>
       </c>
     </row>
     <row r="18">
@@ -619,16 +616,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>0.093605973343014931</v>
+        <v>0.077403060902948809</v>
       </c>
       <c r="C19" s="0">
-        <v>0.094212947302050903</v>
+        <v>0.076886942746758072</v>
       </c>
       <c r="D19" s="0">
-        <v>0.09389048412928469</v>
+        <v>0.077354011756267757</v>
       </c>
       <c r="E19" s="0">
-        <v>0.094326912392283219</v>
+        <v>0.076866474911922486</v>
       </c>
     </row>
     <row r="20">
@@ -636,16 +633,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>0.018416630819574824</v>
+        <v>0.056687431684161932</v>
       </c>
       <c r="C20" s="0">
-        <v>0.007586372855887904</v>
+        <v>0.016903943397127596</v>
       </c>
       <c r="D20" s="0">
-        <v>0.018441641413764094</v>
+        <v>0.056329049367231668</v>
       </c>
       <c r="E20" s="0">
-        <v>0.0075705559008229619</v>
+        <v>0.016338663540226974</v>
       </c>
     </row>
     <row r="21">
@@ -653,16 +650,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>0.50879662511225276</v>
+        <v>1.5056086301808393</v>
       </c>
       <c r="C21" s="0">
-        <v>0.50163123641265062</v>
+        <v>1.5010250588039113</v>
       </c>
       <c r="D21" s="0">
-        <v>0.5058272975925262</v>
+        <v>1.5054920385948152</v>
       </c>
       <c r="E21" s="0">
-        <v>0.50043400477837474</v>
+        <v>1.5009334273401163</v>
       </c>
     </row>
     <row r="22">
@@ -670,16 +667,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>0.49037711338318424</v>
+        <v>1.4489057422092559</v>
       </c>
       <c r="C22" s="0">
-        <v>0.48244155609512523</v>
+        <v>1.4380357534985773</v>
       </c>
       <c r="D22" s="0">
-        <v>0.48738278970443238</v>
+        <v>1.4491469037685289</v>
       </c>
       <c r="E22" s="0">
-        <v>0.48124321217438143</v>
+        <v>1.4379423482441684</v>
       </c>
     </row>
     <row r="23">
@@ -687,16 +684,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>0.51400436468071065</v>
+        <v>0.39396171402600266</v>
       </c>
       <c r="C23" s="0">
-        <v>0.51450488147262663</v>
+        <v>0.39363886680553178</v>
       </c>
       <c r="D23" s="0">
-        <v>0.51424251137042254</v>
+        <v>0.39397589280498074</v>
       </c>
       <c r="E23" s="0">
-        <v>0.51460206471787218</v>
+        <v>0.39363889285738257</v>
       </c>
     </row>
     <row r="24">
@@ -704,16 +701,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>4.02698383552009</v>
+        <v>3.2766084020211443</v>
       </c>
       <c r="C24" s="0">
-        <v>4.030905150530141</v>
+        <v>3.27392325806552</v>
       </c>
       <c r="D24" s="0">
-        <v>4.0288496034704258</v>
+        <v>3.2767263279633783</v>
       </c>
       <c r="E24" s="0">
-        <v>4.0316665358112331</v>
+        <v>3.2739234747406702</v>
       </c>
     </row>
     <row r="25">
@@ -721,16 +718,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>0.10067459588800225</v>
+        <v>0.081915210050528597</v>
       </c>
       <c r="C25" s="0">
-        <v>0.10077262876325353</v>
+        <v>0.081848081451638022</v>
       </c>
       <c r="D25" s="0">
-        <v>0.10072124008676121</v>
+        <v>0.081918158199084462</v>
       </c>
       <c r="E25" s="0">
-        <v>0.10079166339528083</v>
+        <v>0.081848086868516745</v>
       </c>
     </row>
     <row r="26">
@@ -738,16 +735,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>0.18647989092271094</v>
+        <v>0.1387823409522691</v>
       </c>
       <c r="C26" s="0">
-        <v>0.18666147754565615</v>
+        <v>0.13866861037533307</v>
       </c>
       <c r="D26" s="0">
-        <v>0.18656629012818976</v>
+        <v>0.13878733576285179</v>
       </c>
       <c r="E26" s="0">
-        <v>0.18669673545826973</v>
+        <v>0.13866861955271426</v>
       </c>
     </row>
     <row r="27">
@@ -755,16 +752,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
+        <v>0.83333333333333315</v>
+      </c>
+      <c r="C27" s="0">
         <v>0.83333333333333293</v>
       </c>
-      <c r="C27" s="0">
-        <v>0.83333333333333348</v>
-      </c>
       <c r="D27" s="0">
+        <v>0.8333333333333337</v>
+      </c>
+      <c r="E27" s="0">
         <v>0.83333333333333337</v>
-      </c>
-      <c r="E27" s="0">
-        <v>0.83333333333333282</v>
       </c>
     </row>
     <row r="28">
@@ -772,16 +769,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>0.085667394113452047</v>
+        <v>0.06566028567100049</v>
       </c>
       <c r="C28" s="0">
-        <v>0.085750813578770971</v>
+        <v>0.065606477800922144</v>
       </c>
       <c r="D28" s="0">
-        <v>0.085707085228403757</v>
+        <v>0.065662648800830004</v>
       </c>
       <c r="E28" s="0">
-        <v>0.085767010786312325</v>
+        <v>0.065606482142897132</v>
       </c>
     </row>
     <row r="29">
@@ -806,16 +803,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>0.0079385792295628768</v>
+        <v>0.01174277523194831</v>
       </c>
       <c r="C30" s="0">
-        <v>0.0084621337232799361</v>
+        <v>0.011280464945835929</v>
       </c>
       <c r="D30" s="0">
-        <v>0.008183398900880939</v>
+        <v>0.011691362955437747</v>
       </c>
       <c r="E30" s="0">
-        <v>0.008559901605970895</v>
+        <v>0.011259992769025366</v>
       </c>
     </row>
     <row r="31">
@@ -840,16 +837,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>0.041987169852963198</v>
+        <v>4.0182675188718049</v>
       </c>
       <c r="C32" s="0">
-        <v>0.04175760593837876</v>
+        <v>4.1039437027936936</v>
       </c>
       <c r="D32" s="0">
-        <v>0.041865256526868462</v>
+        <v>4.0238265632949428</v>
       </c>
       <c r="E32" s="0">
-        <v>0.041709003161431779</v>
+        <v>4.1067065490517365</v>
       </c>
     </row>
     <row r="33">
@@ -857,16 +854,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>0.050384603823555842</v>
+        <v>4.8219210226461664</v>
       </c>
       <c r="C33" s="0">
-        <v>0.050109127126054503</v>
+        <v>4.9247324433524327</v>
       </c>
       <c r="D33" s="0">
-        <v>0.050238307832242153</v>
+        <v>4.828591875953931</v>
       </c>
       <c r="E33" s="0">
-        <v>0.050050803793718138</v>
+        <v>4.928047858862084</v>
       </c>
     </row>
     <row r="34">
@@ -874,16 +871,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>0.057552898079769425</v>
+        <v>0.066133783422014883</v>
       </c>
       <c r="C34" s="0">
-        <v>0.057715843641439217</v>
+        <v>0.066296337646333178</v>
       </c>
       <c r="D34" s="0">
-        <v>0.057582005397537592</v>
+        <v>0.066122710688721234</v>
       </c>
       <c r="E34" s="0">
-        <v>0.057726316656731461</v>
+        <v>0.066295179120334544</v>
       </c>
     </row>
     <row r="35">
@@ -891,16 +888,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>0</v>
+        <v>0.089359545030377144</v>
       </c>
       <c r="C35" s="0">
-        <v>0</v>
+        <v>0.089286315882192158</v>
       </c>
       <c r="D35" s="0">
-        <v>0</v>
+        <v>0.089362761102379756</v>
       </c>
       <c r="E35" s="0">
-        <v>0</v>
+        <v>0.089286321791348988</v>
       </c>
     </row>
     <row r="36">
@@ -908,16 +905,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>-2.3021159231907768</v>
+        <v>-0.68810709723158303</v>
       </c>
       <c r="C36" s="0">
-        <v>-2.308633745657569</v>
+        <v>-0.68862695176043454</v>
       </c>
       <c r="D36" s="0">
-        <v>-2.3032802159015038</v>
+        <v>-0.68806459785312524</v>
       </c>
       <c r="E36" s="0">
-        <v>-2.3090526662692588</v>
+        <v>-0.68862118276706874</v>
       </c>
     </row>
     <row r="37">
@@ -942,16 +939,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>0.00092371245047243337</v>
+        <v>0.0014326420795254954</v>
       </c>
       <c r="C38" s="0">
-        <v>0.011982626104431912</v>
+        <v>0.046507960493134645</v>
       </c>
       <c r="D38" s="0">
-        <v>0.0055353588984590283</v>
+        <v>0.014098347800862577</v>
       </c>
       <c r="E38" s="0">
-        <v>0.013891403473417191</v>
+        <v>0.05073708144077739</v>
       </c>
     </row>
     <row r="39">
@@ -959,16 +956,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>0.00092083154097874129</v>
+        <v>0.0014171857921040484</v>
       </c>
       <c r="C39" s="0">
-        <v>0.00037931864279439526</v>
+        <v>0.00042259858492818992</v>
       </c>
       <c r="D39" s="0">
-        <v>0.0055324924241292282</v>
+        <v>0.014082262341807917</v>
       </c>
       <c r="E39" s="0">
-        <v>0.0022711667702468882</v>
+        <v>0.0040846658850567435</v>
       </c>
     </row>
     <row r="40">
@@ -993,16 +990,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>1.5389636322717943</v>
+        <v>1.5849419709205088</v>
       </c>
       <c r="C41" s="0">
-        <v>1.5389636322717959</v>
+        <v>1.5849419709205081</v>
       </c>
       <c r="D41" s="0">
-        <v>1.5389636322717954</v>
+        <v>1.5849419709205104</v>
       </c>
       <c r="E41" s="0">
-        <v>1.5389636322717943</v>
+        <v>1.5849419709205093</v>
       </c>
     </row>
     <row r="42">
@@ -1010,16 +1007,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>0.2654861339081046</v>
+        <v>0.47904977341267413</v>
       </c>
       <c r="C42" s="0">
-        <v>0.2661791768273557</v>
+        <v>0.47973592639510576</v>
       </c>
       <c r="D42" s="0">
-        <v>0.26564834779514074</v>
+        <v>0.47899823632570826</v>
       </c>
       <c r="E42" s="0">
-        <v>0.26624054242624123</v>
+        <v>0.4797296547307231</v>
       </c>
     </row>
     <row r="43">
@@ -1027,16 +1024,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>1.2888896127006575</v>
+        <v>1.1148774675169169</v>
       </c>
       <c r="C43" s="0">
-        <v>1.2884314822599963</v>
+        <v>1.1140185648348173</v>
       </c>
       <c r="D43" s="0">
-        <v>1.2887822607959596</v>
+        <v>1.1149420562842223</v>
       </c>
       <c r="E43" s="0">
-        <v>1.2883909823629474</v>
+        <v>1.114026406928935</v>
       </c>
     </row>
     <row r="44">
@@ -1044,16 +1041,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>2.1820843175460252</v>
+        <v>3.3126658405253546</v>
       </c>
       <c r="C44" s="0">
-        <v>2.1555022571662303</v>
+        <v>3.2872438346220321</v>
       </c>
       <c r="D44" s="0">
-        <v>2.1711313025144605</v>
+        <v>3.3113672927653743</v>
       </c>
       <c r="E44" s="0">
-        <v>2.1510856588066711</v>
+        <v>3.28654974472727</v>
       </c>
     </row>
     <row r="45">
@@ -1078,16 +1075,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>0.035101010101010167</v>
+        <v>0.033064516129032252</v>
       </c>
       <c r="C46" s="0">
-        <v>0.035101010101010167</v>
+        <v>0.033064516129032252</v>
       </c>
       <c r="D46" s="0">
-        <v>0.035101010101010167</v>
+        <v>0.033064516129032252</v>
       </c>
       <c r="E46" s="0">
-        <v>0.035101010101010167</v>
+        <v>0.033064516129032252</v>
       </c>
     </row>
     <row r="47">
@@ -1095,16 +1092,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>0.0050724432212038029</v>
+        <v>0.002986042183622827</v>
       </c>
       <c r="C47" s="0">
-        <v>0.0053350924204853415</v>
+        <v>0.002986042183622827</v>
       </c>
       <c r="D47" s="0">
-        <v>0.0051473738312281161</v>
+        <v>0.0027264267990074424</v>
       </c>
       <c r="E47" s="0">
-        <v>0.0052936046112898837</v>
+        <v>0.0027264267990074424</v>
       </c>
     </row>
     <row r="48">
@@ -1112,16 +1109,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>0.025521734698584982</v>
+        <v>0.015677419354838702</v>
       </c>
       <c r="C48" s="0">
-        <v>0.026912476870219283</v>
+        <v>0.015677419354838702</v>
       </c>
       <c r="D48" s="0">
-        <v>0.026101684176134812</v>
+        <v>0.015677419354838702</v>
       </c>
       <c r="E48" s="0">
-        <v>0.027152520084803795</v>
+        <v>0.015677419354838702</v>
       </c>
     </row>
     <row r="49">
@@ -1129,16 +1126,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>0.010101010101010166</v>
+        <v>0.0080645161290322509</v>
       </c>
       <c r="C49" s="0">
-        <v>0.010101010101010166</v>
+        <v>0.0080645161290322509</v>
       </c>
       <c r="D49" s="0">
-        <v>0.010101010101010166</v>
+        <v>0.0080645161290322509</v>
       </c>
       <c r="E49" s="0">
-        <v>0.010101010101010166</v>
+        <v>0.0080645161290322509</v>
       </c>
     </row>
     <row r="50">
@@ -1146,16 +1143,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>0.010147195723533788</v>
+        <v>0.013064516129032252</v>
       </c>
       <c r="C50" s="0">
-        <v>0.010700141406231762</v>
+        <v>0.013064516129032252</v>
       </c>
       <c r="D50" s="0">
-        <v>0.010377778045933117</v>
+        <v>0.013064516129032252</v>
       </c>
       <c r="E50" s="0">
-        <v>0.010795580274681025</v>
+        <v>0.013064516129032252</v>
       </c>
     </row>
     <row r="51">
@@ -1214,16 +1211,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>0.020267802944246373</v>
+        <v>0.019198383854861931</v>
       </c>
       <c r="C54" s="0">
-        <v>0.015079201532185754</v>
+        <v>0.019212241850615264</v>
       </c>
       <c r="D54" s="0">
-        <v>0.018104935495934078</v>
+        <v>0.019196850463049562</v>
       </c>
       <c r="E54" s="0">
-        <v>0.014181317216477869</v>
+        <v>0.019211972637171698</v>
       </c>
     </row>
     <row r="55">
@@ -1265,16 +1262,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>0.0050285668798063631</v>
+        <v>-4.9389319817457409</v>
       </c>
       <c r="C57" s="0">
-        <v>0.0047659176805248246</v>
+        <v>-4.9285259605580558</v>
       </c>
       <c r="D57" s="0">
-        <v>0.00495363626978205</v>
+        <v>-4.9396549591901833</v>
       </c>
       <c r="E57" s="0">
-        <v>0.0048074054897202824</v>
+        <v>-4.9286335661390419</v>
       </c>
     </row>
     <row r="58">
@@ -1282,16 +1279,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>-5.9968223221241548</v>
+        <v>-164.63106605819189</v>
       </c>
       <c r="C58" s="0">
-        <v>-5.9856287006100573</v>
+        <v>-164.28419868526814</v>
       </c>
       <c r="D58" s="0">
-        <v>-5.9952400794864635</v>
+        <v>-164.6551653063394</v>
       </c>
       <c r="E58" s="0">
-        <v>-5.9850993602372204</v>
+        <v>-164.28778553796829</v>
       </c>
     </row>
     <row r="59">
@@ -1299,16 +1296,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>-99.947038702069193</v>
+        <v>0.22044594474004836</v>
       </c>
       <c r="C59" s="0">
-        <v>-99.760478343500793</v>
+        <v>0.22098779215444281</v>
       </c>
       <c r="D59" s="0">
-        <v>-99.920667991440993</v>
+        <v>0.22040903562906958</v>
       </c>
       <c r="E59" s="0">
-        <v>-99.751656003953428</v>
+        <v>0.22098393040111403</v>
       </c>
     </row>
     <row r="60">
@@ -1316,16 +1313,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>0.14388224519928333</v>
+        <v>0.11340577594316675</v>
       </c>
       <c r="C60" s="0">
-        <v>0.14428960910341526</v>
+        <v>0.12597861061066812</v>
       </c>
       <c r="D60" s="0">
-        <v>0.14395501349368622</v>
+        <v>0.11269026965257266</v>
       </c>
       <c r="E60" s="0">
-        <v>0.1443157916416371</v>
+        <v>0.12598215819189523</v>
       </c>
     </row>
     <row r="61">
@@ -1333,16 +1330,16 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>0.04604877932267129</v>
+        <v>-4.601652410435638</v>
       </c>
       <c r="C61" s="0">
-        <v>0.047974200793813551</v>
+        <v>-4.6005668674852309</v>
       </c>
       <c r="D61" s="0">
-        <v>0.046111269720234729</v>
+        <v>-4.6014182054285637</v>
       </c>
       <c r="E61" s="0">
-        <v>0.047976981509983155</v>
+        <v>-4.6004853600298787</v>
       </c>
     </row>
     <row r="62">
@@ -1350,16 +1347,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>-4.5858347056724709</v>
+        <v>-230.08262052178191</v>
       </c>
       <c r="C62" s="0">
-        <v>-4.5895827148680395</v>
+        <v>-230.02834337426231</v>
       </c>
       <c r="D62" s="0">
-        <v>-4.5873177555052731</v>
+        <v>-230.07091027142815</v>
       </c>
       <c r="E62" s="0">
-        <v>-4.5901797990304072</v>
+        <v>-230.02426800149487</v>
       </c>
     </row>
     <row r="63">
@@ -1367,16 +1364,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>-152.86115685574953</v>
+        <v>0.44679772515187544</v>
       </c>
       <c r="C63" s="0">
-        <v>-152.98609049560156</v>
+        <v>0.44643157941095157</v>
       </c>
       <c r="D63" s="0">
-        <v>-152.91059185017571</v>
+        <v>0.44681380551188865</v>
       </c>
       <c r="E63" s="0">
-        <v>-153.00599330101375</v>
+        <v>0.44643160895673584</v>
       </c>
     </row>
     <row r="64">
@@ -1384,16 +1381,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>0.42804657262066625</v>
+        <v>1.7766041018134713</v>
       </c>
       <c r="C64" s="0">
-        <v>0.42846338716927962</v>
+        <v>1.7711955313613008</v>
       </c>
       <c r="D64" s="0">
-        <v>0.42824489364921842</v>
+        <v>1.7764665248996283</v>
       </c>
       <c r="E64" s="0">
-        <v>0.42854431830116774</v>
+        <v>1.7710874071168949</v>
       </c>
     </row>
     <row r="65">
@@ -1401,16 +1398,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>2.675137755745753</v>
+        <v>-3.4762822685648609</v>
       </c>
       <c r="C65" s="0">
-        <v>2.6421934899762838</v>
+        <v>-3.5003522205237143</v>
       </c>
       <c r="D65" s="0">
-        <v>2.6615145314081285</v>
+        <v>-3.4777710230303693</v>
       </c>
       <c r="E65" s="0">
-        <v>2.6367018339966997</v>
+        <v>-3.5010985843348954</v>
       </c>
     </row>
     <row r="66">
@@ -1418,16 +1415,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="0">
-        <v>-0.59147121403898451</v>
+        <v>-434.53528357061282</v>
       </c>
       <c r="C66" s="0">
-        <v>-0.59018028664177979</v>
+        <v>-437.54402756546733</v>
       </c>
       <c r="D66" s="0">
-        <v>-0.59079894516674081</v>
+        <v>-434.72137787879655</v>
       </c>
       <c r="E66" s="0">
-        <v>-0.58991082917146975</v>
+        <v>-437.63732304186414</v>
       </c>
     </row>
     <row r="67">
@@ -1435,16 +1432,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="0">
-        <v>-59.147121403898517</v>
+        <v>1.2861654626443519</v>
       </c>
       <c r="C67" s="0">
-        <v>-59.018028664177812</v>
+        <v>1.2787199847045017</v>
       </c>
       <c r="D67" s="0">
-        <v>-59.079894516674891</v>
+        <v>1.285775910711034</v>
       </c>
       <c r="E67" s="0">
-        <v>-58.991082917146819</v>
+        <v>1.278513614310294</v>
       </c>
     </row>
     <row r="68">
@@ -1452,16 +1449,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="0">
-        <v>21.688931857389026</v>
+        <v>58.219297138495271</v>
       </c>
       <c r="C68" s="0">
-        <v>21.748859928171154</v>
+        <v>57.896995748376973</v>
       </c>
       <c r="D68" s="0">
-        <v>21.719743107899887</v>
+        <v>58.211618759426145</v>
       </c>
       <c r="E68" s="0">
-        <v>21.761299607422139</v>
+        <v>57.890471775252337</v>
       </c>
     </row>
     <row r="69">
@@ -1469,16 +1466,16 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>461.23173654470526</v>
+        <v>-217.80210959487002</v>
       </c>
       <c r="C69" s="0">
-        <v>460.83235682928387</v>
+        <v>-217.90783944888574</v>
       </c>
       <c r="D69" s="0">
-        <v>461.12428245659964</v>
+        <v>-217.82808454962063</v>
       </c>
       <c r="E69" s="0">
-        <v>460.79073199558587</v>
+        <v>-217.91733227376852</v>
       </c>
     </row>
     <row r="70">
@@ -1486,16 +1483,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="0">
-        <v>-130.75836923975888</v>
+        <v>41.755860869520959</v>
       </c>
       <c r="C70" s="0">
-        <v>-130.75616501644703</v>
+        <v>41.693852631205218</v>
       </c>
       <c r="D70" s="0">
-        <v>-130.77631533334679</v>
+        <v>41.750763109039369</v>
       </c>
       <c r="E70" s="0">
-        <v>-130.76410927835093</v>
+        <v>41.691597021428073</v>
       </c>
     </row>
     <row r="71">
@@ -1503,16 +1500,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="0">
-        <v>52.698969449979671</v>
+        <v>658.92742425464996</v>
       </c>
       <c r="C71" s="0">
-        <v>52.799784135295269</v>
+        <v>656.11670926875524</v>
       </c>
       <c r="D71" s="0">
-        <v>52.744392372951218</v>
+        <v>658.80936207287527</v>
       </c>
       <c r="E71" s="0">
-        <v>52.818046052856516</v>
+        <v>656.04732194679389</v>
       </c>
     </row>
     <row r="72">
@@ -1520,16 +1517,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="0">
-        <v>620.90681530661152</v>
+        <v>0.88354642704923714</v>
       </c>
       <c r="C72" s="0">
-        <v>618.6407407696372</v>
+        <v>0.88241916309224033</v>
       </c>
       <c r="D72" s="0">
-        <v>619.9980905984886</v>
+        <v>0.88358821399060461</v>
       </c>
       <c r="E72" s="0">
-        <v>618.27521946179047</v>
+        <v>0.88241304916030594</v>
       </c>
     </row>
     <row r="73">
@@ -1537,16 +1534,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="0">
-        <v>0.74283568028955094</v>
+        <v>0.83402841534261063</v>
       </c>
       <c r="C73" s="0">
-        <v>0.74491110342324462</v>
+        <v>0.83256929332087692</v>
       </c>
       <c r="D73" s="0">
-        <v>0.74375113318731845</v>
+        <v>0.83409679358978217</v>
       </c>
       <c r="E73" s="0">
-        <v>0.74528416713305279</v>
+        <v>0.83256507917067846</v>
       </c>
     </row>
     <row r="74">
@@ -1554,16 +1551,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="0">
-        <v>0.83276452357812925</v>
+        <v>0.3164371149960572</v>
       </c>
       <c r="C74" s="0">
-        <v>0.83387577094342669</v>
+        <v>0.31483514956423503</v>
       </c>
       <c r="D74" s="0">
-        <v>0.83330549942133714</v>
+        <v>0.31642004145793806</v>
       </c>
       <c r="E74" s="0">
-        <v>0.83409761557090012</v>
+        <v>0.31480996051378884</v>
       </c>
     </row>
     <row r="75">
@@ -1571,32 +1568,15 @@
         <v>74</v>
       </c>
       <c r="B75" s="0">
-        <v>0.52881907522851213</v>
+        <v>0</v>
       </c>
       <c r="C75" s="0">
-        <v>0.52892949671178469</v>
+        <v>0</v>
       </c>
       <c r="D75" s="0">
-        <v>0.52899538890412201</v>
+        <v>0</v>
       </c>
       <c r="E75" s="0">
-        <v>0.52900314313212637</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="B76" s="0">
-        <v>0</v>
-      </c>
-      <c r="C76" s="0">
-        <v>0</v>
-      </c>
-      <c r="D76" s="0">
-        <v>0</v>
-      </c>
-      <c r="E76" s="0">
         <v>0</v>
       </c>
     </row>
